--- a/docs/samples/月度台账_202610_示例.xlsx
+++ b/docs/samples/月度台账_202610_示例.xlsx
@@ -11,8 +11,8 @@
     <sheet name="发票明细" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'报销流水'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'发票明细'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'报销流水'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'发票明细'!$A$1:$O$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,6 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,11 +472,6 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>报销状态</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -508,11 +502,6 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>未确定</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -543,11 +532,6 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>未确定</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -578,11 +562,6 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>未确定</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -603,10 +582,9 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:H4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -617,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -633,7 +611,8 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -704,6 +683,11 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>报销状态</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>来源</t>
         </is>
       </c>
@@ -770,6 +754,11 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>未确定</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>pdf</t>
         </is>
       </c>
@@ -836,6 +825,11 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>未确定</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>pdf</t>
         </is>
       </c>
@@ -902,12 +896,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>未确定</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:O4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>